--- a/hardware/boards/handgrip/BOM_handgrip.xlsx
+++ b/hardware/boards/handgrip/BOM_handgrip.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="BOM_Joystick Front_PCB1_2026-07" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="BOM_handgrip_handgrip_2026-09-1" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="79">
   <si>
     <t>No.</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Test-Point</t>
   </si>
   <si>
-    <t>5V,5V,TP1,TP2,TP3,TP4,TP5,TP6,TP7,TP8,TP9,TP10,TP11,TP12,TP13</t>
+    <t>5V,5V</t>
   </si>
   <si>
     <t>Test-Point-0.5mm</t>
@@ -79,6 +79,33 @@
     <t>2</t>
   </si>
   <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>C1,C3,C4,C5,C6,C7,C8,C9,C10,C42</t>
+  </si>
+  <si>
+    <t>C0402</t>
+  </si>
+  <si>
+    <t>CL05B104KO5NNNC</t>
+  </si>
+  <si>
+    <t>SAMSUNG(三星)</t>
+  </si>
+  <si>
+    <t>C1525</t>
+  </si>
+  <si>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t>Capacitance: Tolerance:±10% Tolerance:±10% Voltage Rated: Temperature Coefficient:</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>100uF</t>
   </si>
   <si>
@@ -91,39 +118,12 @@
     <t>CL31A107MQHNNNE</t>
   </si>
   <si>
-    <t>SAMSUNG(三星)</t>
-  </si>
-  <si>
     <t>C15008</t>
   </si>
   <si>
-    <t>LCSC</t>
-  </si>
-  <si>
     <t>Capacitance:100uF Tolerance:±20% Tolerance:±20% Voltage Rating:6.3V Temperature Coefficient:X5R</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>C42</t>
-  </si>
-  <si>
-    <t>C0402</t>
-  </si>
-  <si>
-    <t>CL05B104KO5NNNC</t>
-  </si>
-  <si>
-    <t>C1525</t>
-  </si>
-  <si>
-    <t>Capacitance: Tolerance:±10% Tolerance:±10% Voltage Rated: Temperature Coefficient:</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -151,10 +151,31 @@
     <t>5</t>
   </si>
   <si>
+    <t>SK6805-EC15</t>
+  </si>
+  <si>
+    <t>LED1,LED2,LED3,LED4,LED5,LED6</t>
+  </si>
+  <si>
+    <t>LED-SMD_4P-L1.5-W1.5-BL</t>
+  </si>
+  <si>
+    <t>OPSCO(欧思科)</t>
+  </si>
+  <si>
+    <t>C2890035</t>
+  </si>
+  <si>
+    <t>Dominant Wavelength - R:620nm~625nm Dominant Wavelength - R:620nm~625nm Dominant Wavelength - G:520nm~530nm Dominant Wavelength - G:520nm~530nm Dominant Wavelength - B:460nm~470nm Dominant Wavelength - B:460nm~470nm Data Transmission Rate:800Kbit/s Voltag</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>10kΩ</t>
   </si>
   <si>
-    <t>R40,R41</t>
+    <t>R40</t>
   </si>
   <si>
     <t>R0402</t>
@@ -172,7 +193,7 @@
     <t>Resistance:10000Ω Tolerance:±1% Tolerance:±1% Power(Watts): Overload Voltage (Max): Temperature Coefficient:±100ppm/℃ Temperature Coefficient:±100ppm/℃ Type:Thick Film Resistors Operating Temperature Range:-55℃~+155℃ Operating Temperature Range:-55℃~+155℃</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>B3F-3152</t>
@@ -190,7 +211,25 @@
     <t>Circuit:SPST Actuator Style:Rectangle button Operating Force:150gf Mounting Style:Horizontal Plug Switch Height:3.9mm Contact Current:50mA Voltage Rating (DC):24V With Lamp:- Pin Style:PCPin Mechanical Life:- Operating Temperature:-25℃~+70℃ Operating Temp</t>
   </si>
   <si>
-    <t>7</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>SK6805SIDE-G-003</t>
+  </si>
+  <si>
+    <t>U1,U2,U3</t>
+  </si>
+  <si>
+    <t>LED-SMD_4P-L3.5-W1.6_SK6805SIDE-G-001</t>
+  </si>
+  <si>
+    <t>C31452139</t>
+  </si>
+  <si>
+    <t>Dominant Wavelength - G:520nm~530nm Dominant Wavelength - G:520nm~530nm Data Transmission Rate:800Kbit/s Voltage - Supply:3.7V~5.5V Voltage - Supply:3.7V~5.5V Quiescent Current:0.25mA Lens Color:Translucent Frosted Lens ESD Withstand Voltage:2000V Operati</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>PCA9555APW,118</t>
@@ -585,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="15" width="20" customWidth="1"/>
@@ -643,7 +682,7 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
@@ -690,7 +729,7 @@
         <v>21</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>22</v>
@@ -831,7 +870,7 @@
         <v>45</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -843,28 +882,28 @@
         <v>48</v>
       </c>
       <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
         <v>46</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>49</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>50</v>
-      </c>
-      <c r="I6" t="s">
-        <v>51</v>
       </c>
       <c r="J6" t="s">
         <v>28</v>
       </c>
       <c r="K6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L6" t="s">
         <v>46</v>
       </c>
       <c r="M6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N6" t="s">
         <v>19</v>
@@ -875,43 +914,43 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
         <v>53</v>
       </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>54</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>55</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" t="s">
         <v>56</v>
       </c>
-      <c r="F7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" t="s">
-        <v>54</v>
-      </c>
       <c r="H7" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="I7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J7" t="s">
         <v>28</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N7" t="s">
         <v>19</v>
@@ -922,28 +961,28 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s">
         <v>61</v>
       </c>
-      <c r="E8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" t="s">
-        <v>60</v>
-      </c>
       <c r="H8" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="I8" t="s">
         <v>64</v>
@@ -952,10 +991,10 @@
         <v>28</v>
       </c>
       <c r="K8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M8" t="s">
         <v>65</v>
@@ -967,8 +1006,102 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9" t="s">
+        <v>71</v>
+      </c>
+      <c r="N9" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J10" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10" t="s">
+        <v>73</v>
+      </c>
+      <c r="L10" t="s">
+        <v>73</v>
+      </c>
+      <c r="M10" t="s">
+        <v>78</v>
+      </c>
+      <c r="N10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>19</v>
       </c>
     </row>

--- a/hardware/boards/handgrip/BOM_handgrip.xlsx
+++ b/hardware/boards/handgrip/BOM_handgrip.xlsx
@@ -151,22 +151,22 @@
     <t>5</t>
   </si>
   <si>
-    <t>SK6805-EC15</t>
+    <t>SK6805D-EC2018</t>
   </si>
   <si>
     <t>LED1,LED2,LED3,LED4,LED5,LED6</t>
   </si>
   <si>
-    <t>LED-SMD_4P-L1.5-W1.5-BL</t>
+    <t>LED-SMD_4P-L2.0-W1.8-BL_SK6805D</t>
   </si>
   <si>
     <t>OPSCO(欧思科)</t>
   </si>
   <si>
-    <t>C2890035</t>
-  </si>
-  <si>
-    <t>Dominant Wavelength - R:620nm~625nm Dominant Wavelength - R:620nm~625nm Dominant Wavelength - G:520nm~530nm Dominant Wavelength - G:520nm~530nm Dominant Wavelength - B:460nm~470nm Dominant Wavelength - B:460nm~470nm Data Transmission Rate:800Kbit/s Voltag</t>
+    <t>C5440835</t>
+  </si>
+  <si>
+    <t>Dominant Wavelength - R:620nm~630nm Dominant Wavelength - R:620nm~630nm Dominant Wavelength - G:520nm~535nm Dominant Wavelength - G:520nm~535nm Dominant Wavelength - B:460nm~475nm Dominant Wavelength - B:460nm~475nm Data Transmission Rate:800Kbit/s Voltag</t>
   </si>
   <si>
     <t>6</t>
